--- a/artfynd/A 34396-2023 artfynd.xlsx
+++ b/artfynd/A 34396-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ25"/>
+  <dimension ref="A1:AZ26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2579,10 +2579,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128915345</v>
+        <v>137423111</v>
       </c>
       <c r="B19" t="n">
-        <v>97983</v>
+        <v>98503</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2590,37 +2590,49 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>220686</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) Roth</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Assleröd bränna, Boh</t>
+          <t>Assleröd, Boh</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>330474</v>
+        <v>330351</v>
       </c>
       <c r="R19" t="n">
-        <v>6438708</v>
+        <v>6438714</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2644,22 +2656,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>12:02</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>12:02</t>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>minst 30 st</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2668,30 +2675,31 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Anna Zeffer</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Anna Zeffer</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128915345</t>
+          <t>https://artportalen.se/Sighting/137423111</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128916103</v>
+        <v>128915345</v>
       </c>
       <c r="B20" t="n">
         <v>97983</v>
@@ -2726,13 +2734,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>330449</v>
+        <v>330474</v>
       </c>
       <c r="R20" t="n">
-        <v>6438727</v>
+        <v>6438708</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2761,7 +2769,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2771,7 +2779,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2797,13 +2805,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128916103</t>
+          <t>https://artportalen.se/Sighting/128915345</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128916540</v>
+        <v>128916103</v>
       </c>
       <c r="B21" t="n">
         <v>97983</v>
@@ -2838,13 +2846,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>330284</v>
+        <v>330449</v>
       </c>
       <c r="R21" t="n">
-        <v>6438742</v>
+        <v>6438727</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2873,7 +2881,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2883,7 +2891,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2909,13 +2917,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128916540</t>
+          <t>https://artportalen.se/Sighting/128916103</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129042872</v>
+        <v>128916540</v>
       </c>
       <c r="B22" t="n">
         <v>97983</v>
@@ -2946,17 +2954,17 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Assleröd, Boh</t>
+          <t>Assleröd bränna, Boh</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>330413</v>
+        <v>330284</v>
       </c>
       <c r="R22" t="n">
-        <v>6438980</v>
+        <v>6438742</v>
       </c>
       <c r="S22" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2980,22 +2988,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-10-11</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-10-11</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3010,24 +3018,24 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Mats Eriksson</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Mats Eriksson</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129042872</t>
+          <t>https://artportalen.se/Sighting/128916540</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129043878</v>
+        <v>129042872</v>
       </c>
       <c r="B23" t="n">
         <v>97983</v>
@@ -3055,32 +3063,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Assleröd, Boh</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>330393</v>
+        <v>330413</v>
       </c>
       <c r="R23" t="n">
-        <v>6439061</v>
+        <v>6438980</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3109,7 +3105,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3119,7 +3115,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3128,7 +3124,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3146,13 +3141,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129043878</t>
+          <t>https://artportalen.se/Sighting/129042872</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129044975</v>
+        <v>129043878</v>
       </c>
       <c r="B24" t="n">
         <v>97983</v>
@@ -3180,20 +3175,32 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Assleröd bränna, Assleröd bränna, Boh</t>
+          <t>Assleröd, Boh</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>330281</v>
+        <v>330393</v>
       </c>
       <c r="R24" t="n">
-        <v>6438766</v>
+        <v>6439061</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3222,7 +3229,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3232,7 +3239,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3241,30 +3248,31 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anna Zeffer</t>
+          <t>Mats Eriksson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anna Zeffer</t>
+          <t>Mats Eriksson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129044975</t>
+          <t>https://artportalen.se/Sighting/129043878</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131467465</v>
+        <v>129044975</v>
       </c>
       <c r="B25" t="n">
         <v>97983</v>
@@ -3295,17 +3303,17 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Assleröd , Assleröd , Boh</t>
+          <t>Assleröd bränna, Assleröd bränna, Boh</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>330275</v>
+        <v>330281</v>
       </c>
       <c r="R25" t="n">
-        <v>6438726</v>
+        <v>6438766</v>
       </c>
       <c r="S25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3329,22 +3337,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2025-10-11</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2025-10-11</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3369,6 +3377,118 @@
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129044975</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>131467465</v>
+      </c>
+      <c r="B26" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Assleröd , Assleröd , Boh</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>330275</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6438726</v>
+      </c>
+      <c r="S26" t="n">
+        <v>11</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Västerlanda</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Anna Zeffer</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Anna Zeffer</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/131467465</t>
         </is>
@@ -3400,6 +3520,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34396-2023 artfynd.xlsx
+++ b/artfynd/A 34396-2023 artfynd.xlsx
@@ -2582,7 +2582,7 @@
         <v>137423111</v>
       </c>
       <c r="B19" t="n">
-        <v>98503</v>
+        <v>98504</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 34396-2023 artfynd.xlsx
+++ b/artfynd/A 34396-2023 artfynd.xlsx
@@ -2582,7 +2582,7 @@
         <v>137423111</v>
       </c>
       <c r="B19" t="n">
-        <v>98504</v>
+        <v>98507</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 34396-2023 artfynd.xlsx
+++ b/artfynd/A 34396-2023 artfynd.xlsx
@@ -2582,7 +2582,7 @@
         <v>137423111</v>
       </c>
       <c r="B19" t="n">
-        <v>98507</v>
+        <v>98511</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
